--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.50141980924069</v>
+        <v>3.168980719001613</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04002764959124</v>
+        <v>3.256504493058577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1856197745404948</v>
+        <v>0.03016321336283045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.343462635005249</v>
+        <v>0.05581267818835278</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1301802601597</v>
+        <v>3.108654292275952</v>
       </c>
       <c r="D3" t="n">
-        <v>19.35310237958074</v>
+        <v>3.144879136681871</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1856197745404948</v>
+        <v>0.03016321336283045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.343462635005249</v>
+        <v>0.05581267818835278</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
